--- a/Team-Data/2011-12/4-22-2011-12.xlsx
+++ b/Team-Data/2011-12/4-22-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,37 +728,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
         <v>38</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.594</v>
+        <v>0.603</v>
       </c>
       <c r="H2" t="n">
         <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K2" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L2" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.369</v>
+        <v>0.364</v>
       </c>
       <c r="O2" t="n">
         <v>15.7</v>
@@ -700,22 +767,22 @@
         <v>21.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.739</v>
+        <v>0.74</v>
       </c>
       <c r="R2" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
         <v>31.3</v>
       </c>
       <c r="T2" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U2" t="n">
         <v>22.3</v>
       </c>
       <c r="V2" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W2" t="n">
         <v>8.1</v>
@@ -733,19 +800,19 @@
         <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.3</v>
+        <v>96</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG2" t="n">
         <v>9</v>
@@ -760,22 +827,22 @@
         <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>23</v>
@@ -784,16 +851,16 @@
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
         <v>10</v>
@@ -802,7 +869,7 @@
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -811,7 +878,7 @@
         <v>19</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>10</v>
@@ -933,7 +1000,7 @@
         <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -945,13 +1012,13 @@
         <v>5</v>
       </c>
       <c r="AL3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM3" t="n">
         <v>24</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
         <v>23</v>
@@ -987,16 +1054,16 @@
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -1025,49 +1092,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="J4" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.415</v>
+        <v>0.414</v>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
         <v>13.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.294</v>
+        <v>0.297</v>
       </c>
       <c r="O4" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R4" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S4" t="n">
         <v>28.7</v>
@@ -1076,10 +1143,10 @@
         <v>39</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W4" t="n">
         <v>6.1</v>
@@ -1100,10 +1167,10 @@
         <v>87.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.7</v>
+        <v>-13.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1127,7 +1194,7 @@
         <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM4" t="n">
         <v>27</v>
@@ -1139,13 +1206,13 @@
         <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
         <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1154,7 +1221,7 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
@@ -1169,7 +1236,7 @@
         <v>26</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
         <v>12</v>
@@ -1342,7 +1409,7 @@
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" t="n">
         <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1407,7 +1474,7 @@
         <v>34.3</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.423</v>
@@ -1419,34 +1486,34 @@
         <v>19.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O6" t="n">
         <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.717</v>
+        <v>0.718</v>
       </c>
       <c r="R6" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S6" t="n">
         <v>29.7</v>
       </c>
       <c r="T6" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X6" t="n">
         <v>4</v>
@@ -1458,28 +1525,28 @@
         <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6.7</v>
+        <v>-6.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
         <v>26</v>
       </c>
       <c r="AH6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI6" t="n">
         <v>29</v>
@@ -1497,7 +1564,7 @@
         <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1518,7 +1585,7 @@
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV6" t="n">
         <v>26</v>
@@ -1533,13 +1600,13 @@
         <v>28</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1728,7 @@
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
         <v>18</v>
@@ -1682,7 +1749,7 @@
         <v>19</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
         <v>26</v>
@@ -1694,7 +1761,7 @@
         <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -1724,7 +1791,7 @@
         <v>19</v>
       </c>
       <c r="BC7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
       </c>
       <c r="I8" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J8" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L8" t="n">
         <v>6.6</v>
@@ -1786,10 +1853,10 @@
         <v>0.33</v>
       </c>
       <c r="O8" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="P8" t="n">
-        <v>26.7</v>
+        <v>27</v>
       </c>
       <c r="Q8" t="n">
         <v>0.737</v>
@@ -1804,7 +1871,7 @@
         <v>43</v>
       </c>
       <c r="U8" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V8" t="n">
         <v>15.4</v>
@@ -1816,34 +1883,34 @@
         <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Z8" t="n">
         <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB8" t="n">
         <v>103.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
         <v>5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>6</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1852,13 +1919,13 @@
         <v>15</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>16</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
         <v>24</v>
@@ -1888,7 +1955,7 @@
         <v>25</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>15</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -1935,58 +2002,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
         <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>0.375</v>
+        <v>0.365</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J9" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M9" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P9" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="R9" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S9" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T9" t="n">
         <v>40.2</v>
       </c>
       <c r="U9" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="V9" t="n">
         <v>15.7</v>
@@ -1998,22 +2065,22 @@
         <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.5</v>
+        <v>90.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.2</v>
+        <v>-5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
@@ -2025,13 +2092,13 @@
         <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI9" t="n">
         <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
         <v>25</v>
@@ -2043,19 +2110,19 @@
         <v>26</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2079,10 +2146,10 @@
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>0.359</v>
+        <v>0.349</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J10" t="n">
-        <v>82.5</v>
+        <v>82.3</v>
       </c>
       <c r="K10" t="n">
         <v>0.457</v>
@@ -2147,55 +2214,55 @@
         <v>20.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="O10" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="P10" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.771</v>
+        <v>0.773</v>
       </c>
       <c r="R10" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T10" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="U10" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V10" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W10" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X10" t="n">
         <v>5.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,16 +2274,16 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
         <v>7</v>
       </c>
       <c r="AJ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK10" t="n">
         <v>9</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>8</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2234,31 +2301,31 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT10" t="n">
         <v>28</v>
       </c>
       <c r="AU10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
         <v>6</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
         <v>33</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
-        <v>0.508</v>
+        <v>0.516</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
@@ -2317,7 +2384,7 @@
         <v>37.8</v>
       </c>
       <c r="J11" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K11" t="n">
         <v>0.451</v>
@@ -2332,16 +2399,16 @@
         <v>0.36</v>
       </c>
       <c r="O11" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q11" t="n">
         <v>0.782</v>
       </c>
       <c r="R11" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S11" t="n">
         <v>30.4</v>
@@ -2362,7 +2429,7 @@
         <v>4.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z11" t="n">
         <v>20.4</v>
@@ -2371,22 +2438,22 @@
         <v>18.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
         <v>3</v>
@@ -2404,13 +2471,13 @@
         <v>10</v>
       </c>
       <c r="AM11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN11" t="n">
         <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>28</v>
@@ -2425,16 +2492,16 @@
         <v>18</v>
       </c>
       <c r="AT11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU11" t="n">
         <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
         <v>19</v>
@@ -2449,7 +2516,7 @@
         <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2604,7 +2671,7 @@
         <v>7</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
         <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>0.625</v>
+        <v>0.619</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,28 +2748,28 @@
         <v>37</v>
       </c>
       <c r="J13" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L13" t="n">
         <v>7.7</v>
       </c>
       <c r="M13" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O13" t="n">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="R13" t="n">
         <v>12.2</v>
@@ -2714,13 +2781,13 @@
         <v>41.7</v>
       </c>
       <c r="U13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
         <v>13.3</v>
       </c>
       <c r="W13" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X13" t="n">
         <v>4.8</v>
@@ -2729,19 +2796,19 @@
         <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2753,7 +2820,7 @@
         <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI13" t="n">
         <v>13</v>
@@ -2765,19 +2832,19 @@
         <v>10</v>
       </c>
       <c r="AL13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
         <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
@@ -2789,7 +2856,7 @@
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU13" t="n">
         <v>13</v>
@@ -2804,10 +2871,10 @@
         <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -2845,28 +2912,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
         <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.631</v>
+        <v>0.625</v>
       </c>
       <c r="H14" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="I14" t="n">
         <v>36.7</v>
       </c>
       <c r="J14" t="n">
-        <v>80.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="K14" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L14" t="n">
         <v>5.5</v>
@@ -2878,22 +2945,22 @@
         <v>0.324</v>
       </c>
       <c r="O14" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P14" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="R14" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="S14" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="T14" t="n">
-        <v>46.3</v>
+        <v>46</v>
       </c>
       <c r="U14" t="n">
         <v>22.4</v>
@@ -2902,13 +2969,13 @@
         <v>15.1</v>
       </c>
       <c r="W14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z14" t="n">
         <v>16.8</v>
@@ -2917,16 +2984,16 @@
         <v>20.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI14" t="n">
         <v>15</v>
@@ -2944,7 +3011,7 @@
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL14" t="n">
         <v>23</v>
@@ -2962,10 +3029,10 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2986,7 +3053,7 @@
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -3105,10 +3172,10 @@
         <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF15" t="n">
         <v>8</v>
@@ -3117,13 +3184,13 @@
         <v>8</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK15" t="n">
         <v>16</v>
@@ -3138,28 +3205,28 @@
         <v>25</v>
       </c>
       <c r="AO15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU15" t="n">
         <v>24</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.719</v>
+        <v>0.714</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
@@ -3227,10 +3294,10 @@
         <v>37.4</v>
       </c>
       <c r="J16" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L16" t="n">
         <v>5.6</v>
@@ -3239,7 +3306,7 @@
         <v>15.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O16" t="n">
         <v>19</v>
@@ -3248,19 +3315,19 @@
         <v>24.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R16" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
         <v>31.3</v>
       </c>
       <c r="T16" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U16" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V16" t="n">
         <v>14.9</v>
@@ -3269,46 +3336,46 @@
         <v>8.9</v>
       </c>
       <c r="X16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y16" t="n">
         <v>4.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA16" t="n">
         <v>20.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC16" t="n">
         <v>6.9</v>
       </c>
       <c r="AD16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" t="n">
         <v>5</v>
       </c>
-      <c r="AE16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>6</v>
-      </c>
       <c r="AI16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>20</v>
@@ -3320,13 +3387,13 @@
         <v>9</v>
       </c>
       <c r="AO16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP16" t="n">
         <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
@@ -3335,10 +3402,10 @@
         <v>12</v>
       </c>
       <c r="AT16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU16" t="n">
         <v>18</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>19</v>
       </c>
       <c r="AV16" t="n">
         <v>18</v>
@@ -3353,10 +3420,10 @@
         <v>3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3514,7 +3581,7 @@
         <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT17" t="n">
         <v>14</v>
@@ -3532,13 +3599,13 @@
         <v>16</v>
       </c>
       <c r="AY17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -3573,37 +3640,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
         <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J18" t="n">
         <v>82.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L18" t="n">
         <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="O18" t="n">
         <v>19.5</v>
@@ -3612,16 +3679,16 @@
         <v>25.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="R18" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S18" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T18" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U18" t="n">
         <v>19.5</v>
@@ -3630,7 +3697,7 @@
         <v>15.2</v>
       </c>
       <c r="W18" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X18" t="n">
         <v>4.4</v>
@@ -3639,19 +3706,19 @@
         <v>5.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
         <v>21</v>
@@ -3663,16 +3730,16 @@
         <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="n">
         <v>12</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
         <v>11</v>
@@ -3681,7 +3748,7 @@
         <v>6</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
         <v>4</v>
@@ -3690,7 +3757,7 @@
         <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
         <v>9</v>
@@ -3699,19 +3766,19 @@
         <v>8</v>
       </c>
       <c r="AT18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU18" t="n">
         <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>26</v>
       </c>
       <c r="AX18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>-5.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH19" t="n">
         <v>27</v>
@@ -3857,13 +3924,13 @@
         <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
         <v>3</v>
       </c>
       <c r="AN19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
@@ -3872,10 +3939,10 @@
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3887,10 +3954,10 @@
         <v>22</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX19" t="n">
         <v>29</v>
@@ -3902,7 +3969,7 @@
         <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" t="n">
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>0.313</v>
+        <v>0.317</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,34 +4022,34 @@
         <v>35</v>
       </c>
       <c r="J20" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
         <v>11.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O20" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P20" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R20" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T20" t="n">
         <v>41.1</v>
@@ -4003,31 +4070,31 @@
         <v>5.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>89.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.8</v>
+        <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4036,16 +4103,16 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
         <v>20</v>
@@ -4078,13 +4145,13 @@
         <v>22</v>
       </c>
       <c r="AY20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA20" t="n">
         <v>24</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>23</v>
       </c>
       <c r="BB20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -4119,55 +4186,55 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F21" t="n">
         <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>0.531</v>
+        <v>0.524</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J21" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M21" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.335</v>
+        <v>0.331</v>
       </c>
       <c r="O21" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P21" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q21" t="n">
         <v>0.743</v>
       </c>
       <c r="R21" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S21" t="n">
         <v>30.5</v>
       </c>
       <c r="T21" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U21" t="n">
         <v>20</v>
@@ -4176,7 +4243,7 @@
         <v>16.2</v>
       </c>
       <c r="W21" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X21" t="n">
         <v>4.2</v>
@@ -4191,43 +4258,43 @@
         <v>21.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.7</v>
+        <v>97.5</v>
       </c>
       <c r="AC21" t="n">
         <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ21" t="n">
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM21" t="n">
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
         <v>7</v>
@@ -4245,7 +4312,7 @@
         <v>17</v>
       </c>
       <c r="AT21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU21" t="n">
         <v>23</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -4301,70 +4368,70 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
         <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.719</v>
+        <v>0.73</v>
       </c>
       <c r="H22" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="I22" t="n">
         <v>37.3</v>
       </c>
       <c r="J22" t="n">
-        <v>79.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.471</v>
+        <v>0.473</v>
       </c>
       <c r="L22" t="n">
         <v>7.1</v>
       </c>
       <c r="M22" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N22" t="n">
         <v>0.356</v>
       </c>
       <c r="O22" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="P22" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.803</v>
+        <v>0.802</v>
       </c>
       <c r="R22" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S22" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U22" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="V22" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W22" t="n">
         <v>7.6</v>
       </c>
       <c r="X22" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z22" t="n">
         <v>20.3</v>
@@ -4373,16 +4440,16 @@
         <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.9</v>
+        <v>102.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
@@ -4391,25 +4458,25 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL22" t="n">
         <v>12</v>
       </c>
       <c r="AM22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4424,7 +4491,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -4483,55 +4550,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E23" t="n">
         <v>36</v>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J23" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L23" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="M23" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="O23" t="n">
         <v>15.1</v>
       </c>
       <c r="P23" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.658</v>
+        <v>0.657</v>
       </c>
       <c r="R23" t="n">
         <v>11.2</v>
       </c>
       <c r="S23" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T23" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="U23" t="n">
         <v>20.1</v>
@@ -4543,7 +4610,7 @@
         <v>6.8</v>
       </c>
       <c r="X23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
         <v>4.1</v>
@@ -4555,28 +4622,28 @@
         <v>19.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.3</v>
+        <v>94.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>11</v>
       </c>
       <c r="AF23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="n">
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
@@ -4606,16 +4673,16 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW23" t="n">
         <v>25</v>
@@ -4636,7 +4703,7 @@
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>4.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF24" t="n">
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>17</v>
@@ -4958,13 +5025,13 @@
         <v>16</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
@@ -4973,7 +5040,7 @@
         <v>16</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
@@ -4997,7 +5064,7 @@
         <v>15</v>
       </c>
       <c r="BB25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5119,7 +5186,7 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
@@ -5131,13 +5198,13 @@
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM26" t="n">
         <v>8</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
         <v>10</v>
@@ -5173,10 +5240,10 @@
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -5211,34 +5278,34 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
         <v>43</v>
       </c>
       <c r="G27" t="n">
-        <v>0.328</v>
+        <v>0.317</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J27" t="n">
         <v>86.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.433</v>
+        <v>0.431</v>
       </c>
       <c r="L27" t="n">
         <v>6.3</v>
       </c>
       <c r="M27" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
         <v>0.316</v>
@@ -5247,7 +5314,7 @@
         <v>17.1</v>
       </c>
       <c r="P27" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0.736</v>
@@ -5259,16 +5326,16 @@
         <v>29.5</v>
       </c>
       <c r="T27" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U27" t="n">
         <v>19.2</v>
       </c>
       <c r="V27" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W27" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X27" t="n">
         <v>4.8</v>
@@ -5277,22 +5344,22 @@
         <v>6.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF27" t="n">
         <v>27</v>
@@ -5301,31 +5368,31 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
         <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AN27" t="n">
         <v>29</v>
       </c>
       <c r="AO27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
         <v>25</v>
@@ -5337,7 +5404,7 @@
         <v>25</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
@@ -5349,22 +5416,22 @@
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.746</v>
+        <v>0.742</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="J28" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
@@ -5426,19 +5493,19 @@
         <v>0.393</v>
       </c>
       <c r="O28" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P28" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R28" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S28" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T28" t="n">
         <v>42.7</v>
@@ -5459,19 +5526,19 @@
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
         <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.2</v>
+        <v>103</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
         <v>18</v>
@@ -5513,13 +5580,13 @@
         <v>20</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
         <v>5</v>
@@ -5531,10 +5598,10 @@
         <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E29" t="n">
         <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G29" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J29" t="n">
         <v>78</v>
       </c>
       <c r="K29" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L29" t="n">
         <v>5.5</v>
@@ -5608,13 +5675,13 @@
         <v>0.337</v>
       </c>
       <c r="O29" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P29" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
@@ -5629,7 +5696,7 @@
         <v>20.9</v>
       </c>
       <c r="V29" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W29" t="n">
         <v>6.5</v>
@@ -5644,28 +5711,28 @@
         <v>23.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>90.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AC29" t="n">
         <v>-3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>28</v>
@@ -5674,7 +5741,7 @@
         <v>28</v>
       </c>
       <c r="AK29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
@@ -5686,13 +5753,13 @@
         <v>20</v>
       </c>
       <c r="AO29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP29" t="n">
         <v>19</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
         <v>23</v>
@@ -5716,19 +5783,19 @@
         <v>18</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>27</v>
       </c>
       <c r="BC29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>0.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>14</v>
@@ -5847,7 +5914,7 @@
         <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
@@ -5856,7 +5923,7 @@
         <v>4</v>
       </c>
       <c r="AK30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL30" t="n">
         <v>28</v>
@@ -5874,7 +5941,7 @@
         <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
         <v>3</v>
@@ -5883,7 +5950,7 @@
         <v>15</v>
       </c>
       <c r="AT30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU30" t="n">
         <v>11</v>
@@ -5892,7 +5959,7 @@
         <v>12</v>
       </c>
       <c r="AW30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX30" t="n">
         <v>4</v>
@@ -5904,7 +5971,7 @@
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6059,7 +6126,7 @@
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS31" t="n">
         <v>20</v>
@@ -6071,7 +6138,7 @@
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>15</v>
@@ -6083,7 +6150,7 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA31" t="n">
         <v>22</v>
@@ -6092,7 +6159,7 @@
         <v>24</v>
       </c>
       <c r="BC31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-22-2011-12</t>
+          <t>2012-04-22</t>
         </is>
       </c>
     </row>
